--- a/artfynd/A 1374-2025 artfynd.xlsx
+++ b/artfynd/A 1374-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2775,6 +2775,297 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127008551</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rösåsen, Rösåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>536870</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6701508</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Torsång</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127008286</v>
+      </c>
+      <c r="B20" t="n">
+        <v>88517</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>239209</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kantarellvaxing</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hygrocybe cantharellus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Rösåsen, Rösåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>536862</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6701563</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Torsång</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127008641</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92607</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rösåsen, Rösåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>536863</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6701510</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Torsång</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1374-2025 artfynd.xlsx
+++ b/artfynd/A 1374-2025 artfynd.xlsx
@@ -2780,7 +2780,7 @@
         <v>127008551</v>
       </c>
       <c r="B19" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127008286</v>
       </c>
       <c r="B20" t="n">
-        <v>88517</v>
+        <v>88518</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>127008641</v>
       </c>
       <c r="B21" t="n">
-        <v>92607</v>
+        <v>92608</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 1374-2025 artfynd.xlsx
+++ b/artfynd/A 1374-2025 artfynd.xlsx
@@ -2780,7 +2780,7 @@
         <v>127008551</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127008286</v>
       </c>
       <c r="B20" t="n">
-        <v>88518</v>
+        <v>88522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>127008641</v>
       </c>
       <c r="B21" t="n">
-        <v>92608</v>
+        <v>92612</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 1374-2025 artfynd.xlsx
+++ b/artfynd/A 1374-2025 artfynd.xlsx
@@ -2780,7 +2780,7 @@
         <v>127008551</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 1374-2025 artfynd.xlsx
+++ b/artfynd/A 1374-2025 artfynd.xlsx
@@ -2780,7 +2780,7 @@
         <v>127008551</v>
       </c>
       <c r="B19" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127008286</v>
       </c>
       <c r="B20" t="n">
-        <v>88522</v>
+        <v>88524</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>127008641</v>
       </c>
       <c r="B21" t="n">
-        <v>92612</v>
+        <v>92614</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 1374-2025 artfynd.xlsx
+++ b/artfynd/A 1374-2025 artfynd.xlsx
@@ -2780,7 +2780,7 @@
         <v>127008551</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127008286</v>
       </c>
       <c r="B20" t="n">
-        <v>88524</v>
+        <v>88530</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>127008641</v>
       </c>
       <c r="B21" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 1374-2025 artfynd.xlsx
+++ b/artfynd/A 1374-2025 artfynd.xlsx
@@ -2780,7 +2780,7 @@
         <v>127008551</v>
       </c>
       <c r="B19" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127008286</v>
       </c>
       <c r="B20" t="n">
-        <v>88530</v>
+        <v>88533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>127008641</v>
       </c>
       <c r="B21" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 1374-2025 artfynd.xlsx
+++ b/artfynd/A 1374-2025 artfynd.xlsx
@@ -2780,7 +2780,7 @@
         <v>127008551</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127008286</v>
       </c>
       <c r="B20" t="n">
-        <v>88533</v>
+        <v>88541</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>127008641</v>
       </c>
       <c r="B21" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 1374-2025 artfynd.xlsx
+++ b/artfynd/A 1374-2025 artfynd.xlsx
@@ -2780,7 +2780,7 @@
         <v>127008551</v>
       </c>
       <c r="B19" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127008286</v>
       </c>
       <c r="B20" t="n">
-        <v>88541</v>
+        <v>88542</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>127008641</v>
       </c>
       <c r="B21" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 1374-2025 artfynd.xlsx
+++ b/artfynd/A 1374-2025 artfynd.xlsx
@@ -2780,7 +2780,7 @@
         <v>127008551</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127008286</v>
       </c>
       <c r="B20" t="n">
-        <v>88542</v>
+        <v>88543</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>127008641</v>
       </c>
       <c r="B21" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
